--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
@@ -60,7 +60,7 @@
     <x:numFmt numFmtId="0" formatCode=""/>
     <x:numFmt numFmtId="1" formatCode="$ #,##0"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="4">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -70,6 +70,20 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
@@ -732,11 +732,11 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="3" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.270624999999999" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="10.410625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.700625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11.270625" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="9.550625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="7.980625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.000625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="8.580625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="10.140625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="8.280625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:8">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
@@ -290,146 +290,146 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="23">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="6" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="6" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="18">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
@@ -739,31 +739,10 @@
     <x:col min="8" max="8" width="8.280625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8">
-      <x:c r="B1" s="0" t="s"/>
-      <x:c r="C1" s="0" t="s"/>
-    </x:row>
-    <x:row r="2" spans="1:8">
-      <x:c r="B2" s="0" t="s"/>
-      <x:c r="C2" s="0" t="s"/>
-      <x:c r="D2" s="0" t="s"/>
-      <x:c r="E2" s="0" t="s"/>
-      <x:c r="F2" s="0" t="s"/>
-      <x:c r="G2" s="0" t="s"/>
-      <x:c r="H2" s="0" t="s"/>
-    </x:row>
-    <x:row r="3" spans="1:8">
-      <x:c r="B3" s="0" t="s"/>
-      <x:c r="C3" s="0" t="s"/>
-      <x:c r="D3" s="0" t="s"/>
-      <x:c r="E3" s="0" t="s"/>
-      <x:c r="F3" s="0" t="s"/>
-      <x:c r="G3" s="0" t="s"/>
-      <x:c r="H3" s="0" t="s"/>
-    </x:row>
+    <x:row r="1" spans="1:8"/>
+    <x:row r="2" spans="1:8"/>
+    <x:row r="3" spans="1:8"/>
     <x:row r="4" spans="1:8">
-      <x:c r="B4" s="0" t="s"/>
-      <x:c r="C4" s="0" t="s"/>
       <x:c r="D4" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -773,8 +752,6 @@
       <x:c r="H4" s="3" t="s"/>
     </x:row>
     <x:row r="5" spans="1:8">
-      <x:c r="B5" s="0" t="s"/>
-      <x:c r="C5" s="0" t="s"/>
       <x:c r="D5" s="15" t="s">
         <x:v>1</x:v>
       </x:c>
@@ -792,8 +769,6 @@
       </x:c>
     </x:row>
     <x:row r="6" spans="1:8">
-      <x:c r="B6" s="0" t="s"/>
-      <x:c r="C6" s="0" t="s"/>
       <x:c r="D6" s="7" t="s">
         <x:v>6</x:v>
       </x:c>
@@ -811,8 +786,6 @@
       </x:c>
     </x:row>
     <x:row r="7" spans="1:8">
-      <x:c r="B7" s="0" t="s"/>
-      <x:c r="C7" s="0" t="s"/>
       <x:c r="D7" s="7" t="s">
         <x:v>8</x:v>
       </x:c>
@@ -830,8 +803,6 @@
       </x:c>
     </x:row>
     <x:row r="8" spans="1:8">
-      <x:c r="B8" s="0" t="s"/>
-      <x:c r="C8" s="0" t="s"/>
       <x:c r="D8" s="11" t="s">
         <x:v>10</x:v>
       </x:c>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/ShiftingRanges.xlsx
@@ -58,7 +58,7 @@
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="2">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="1" formatCode="$ #,##0"/>
+    <x:numFmt numFmtId="165" formatCode="$ #,##0"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -320,7 +320,7 @@
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -332,7 +332,7 @@
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -401,7 +401,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -417,7 +417,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
